--- a/AAII_Financials/Quarterly/AFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>AFL</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4117000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4346000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4866000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4740000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4160000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3398000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5403000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2949000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5138000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5436000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3778000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4950000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5172000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4800000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3952000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4708000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5332000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5173000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5436000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5237000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5564000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5869000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5913000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5665000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5407000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5162000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5613000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5554000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5513000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5659000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5190000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5582000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5594000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5471000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5434000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5514000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5437000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5319000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5969000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>5738000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2290000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2367000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1908000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2482000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2401000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2383000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2060000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2375000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2480000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2566000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2311000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2568000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2635000</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>194000</v>
       </c>
       <c r="R9" s="3">
         <v>194000</v>
       </c>
       <c r="S9" s="3">
+        <v>194000</v>
+      </c>
+      <c r="T9" s="3">
         <v>197000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>207000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>301000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>278000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>280000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>311000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>300000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>292000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>289000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>333000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>315000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>317000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>309000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>340000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>313000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>315000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>303000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>314000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>284000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>271000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>283000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>294000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>283000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>282000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1808000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2056000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2499000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2832000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1678000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>997000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3020000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>889000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2763000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2956000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1212000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2639000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2604000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2165000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3758000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4514000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5135000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4966000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5135000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4959000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5284000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5558000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5613000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5373000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5118000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4829000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5298000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5237000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5204000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5319000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4877000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5267000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5291000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5157000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5150000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>5243000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>5154000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>5025000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>5686000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5456000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,18 +1514,18 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>4000</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>4000</v>
       </c>
       <c r="S14" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T14" s="3">
         <v>17000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1531,85 +1550,88 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>10000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>18000</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>2000</v>
       </c>
       <c r="AF14" s="3">
         <v>2000</v>
       </c>
       <c r="AG14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH14" s="3">
         <v>64000</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>5000</v>
       </c>
       <c r="AI14" s="3">
         <v>5000</v>
       </c>
       <c r="AJ14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AK14" s="3">
         <v>7000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>10000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>8000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>9000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>10000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>14000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>11300</v>
       </c>
       <c r="O15" s="3">
         <v>11300</v>
@@ -1618,7 +1640,7 @@
         <v>11300</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3058000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3061000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3233000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2689000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3286000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3203000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3218000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2807000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3069000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3219000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3441000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3096000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3296000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3410000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3359000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3320000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3569000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3823000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4147000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4067000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4129000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4204000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4635000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4449000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4274000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4387000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4499000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4461000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4347000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4359000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4410000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4383000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4409000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4433000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4376000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4380000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4331000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4359000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4744000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4710000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1059000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1285000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1633000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2051000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>874000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>195000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2185000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>142000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2069000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2217000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>337000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1854000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1876000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1390000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>593000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1388000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1763000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1350000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1289000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1170000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1435000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1665000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1278000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1216000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1133000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>775000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1114000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1093000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1166000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1300000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>780000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1199000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1185000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1038000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1058000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1134000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1106000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>960000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1225000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1028000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,8 +2101,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2146,113 +2179,116 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1067000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1292000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1648000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2058000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>882000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>201000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2217000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>146000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2072000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2218000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>346800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1865300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1887300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1401300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>593000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1388000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1763000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1350000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1289000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1170000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1435000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1665000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1278000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1216000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1133000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>775000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1114000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1093000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1166000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1300000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>780000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1199000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1185000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1038000</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2268,25 +2304,28 @@
       <c r="AP21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E22" s="3">
         <v>60000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>61000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>57000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>52000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>50000</v>
       </c>
       <c r="I22" s="3">
         <v>50000</v>
@@ -2298,58 +2337,58 @@
         <v>50000</v>
       </c>
       <c r="L22" s="3">
-        <v>47000</v>
+        <v>50000</v>
       </c>
       <c r="M22" s="3">
         <v>47000</v>
       </c>
       <c r="N22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="O22" s="3">
         <v>49000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>51000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>48000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>55000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>59000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>55000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>56000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>57000</v>
       </c>
       <c r="V22" s="3">
         <v>57000</v>
       </c>
       <c r="W22" s="3">
-        <v>62000</v>
+        <v>57000</v>
       </c>
       <c r="X22" s="3">
         <v>62000</v>
       </c>
       <c r="Y22" s="3">
+        <v>62000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>61000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>63000</v>
       </c>
       <c r="AA22" s="3">
         <v>63000</v>
       </c>
       <c r="AB22" s="3">
+        <v>63000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>55000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>57000</v>
       </c>
       <c r="AD22" s="3">
         <v>57000</v>
@@ -2358,284 +2397,293 @@
         <v>57000</v>
       </c>
       <c r="AF22" s="3">
-        <v>58000</v>
+        <v>57000</v>
       </c>
       <c r="AG22" s="3">
         <v>58000</v>
       </c>
       <c r="AH22" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>53000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>54000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>59000</v>
       </c>
       <c r="AL22" s="3">
         <v>59000</v>
       </c>
       <c r="AM22" s="3">
+        <v>59000</v>
+      </c>
+      <c r="AN22" s="3">
         <v>61000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>62000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>72000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>995000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1225000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1572000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1994000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>822000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>145000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2135000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>92000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2019000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2170000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>290000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1805000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1825000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1342000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>538000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1329000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1708000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1294000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1232000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1113000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1373000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1603000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1217000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1153000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1070000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>720000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1057000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1036000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1109000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1242000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>722000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1146000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1131000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>982000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>999000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1075000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1045000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>898000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1153000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E24" s="3">
         <v>206000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>193000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>355000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>223000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>116000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>233000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>185000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>264000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>291000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>236000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>191000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>154000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>342000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-452000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>314000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>247000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>193000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>225000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>268000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>310000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>265000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1303000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>265000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>154000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>276000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>259000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>292000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>314000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>190000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>290000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>265000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>349000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>359000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>332000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>306000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>402000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>825000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1019000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1379000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1639000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>599000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>29000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1902000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-93000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1755000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1879000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>268000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1569000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1634000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1188000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>196000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1781000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1394000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1047000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1039000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>888000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1105000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1293000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>952000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2456000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>805000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>566000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>781000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>777000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>817000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>928000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>532000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>856000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>832000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>717000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>650000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>716000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>713000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>592000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>751000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>629000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>825000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1019000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1379000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1639000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>599000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1902000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-93000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1755000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1879000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>268000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1569000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1634000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1188000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>196000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1781000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1394000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1047000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1039000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>888000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1105000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1293000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>952000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2456000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>805000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>566000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>781000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>777000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>817000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>928000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>532000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>856000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>832000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>717000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>650000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>716000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>713000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>592000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>751000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>629000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,17 +3256,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3214,24 +3274,24 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>1933000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,8 +3601,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>825000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1019000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1379000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1639000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>599000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1902000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-93000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1755000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1879000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>268000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1569000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1634000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1188000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>196000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1781000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1394000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1047000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1039000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>888000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1105000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1293000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>952000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2456000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>805000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>566000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>781000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>777000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>817000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>928000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>525000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>845000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>832000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>717000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2583000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>716000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>713000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>592000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>751000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>629000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>825000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1019000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1379000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1639000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>599000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1902000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-93000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1755000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1879000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>268000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1569000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1634000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1188000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>196000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1781000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1394000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1047000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1039000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>888000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1105000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1293000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>952000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2456000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>805000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>566000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>781000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>777000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>817000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>928000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>525000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>845000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>832000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>717000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2583000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>716000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>713000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>592000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>751000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>629000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6120000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5654000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6245000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6768000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6965000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5231000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6229000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5612000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6060000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5098000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4306000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5502000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4720000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3809000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3943000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4710000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5173000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4275000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5051000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6208000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5469000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4990000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5141000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5563000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5528000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4148000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4896000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4216000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3019000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3892000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4337000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3429000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3847000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4080000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3491000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4927000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4264000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4205000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4859000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>5270000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2815000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2616000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1387000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2362000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2389000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2264000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1599000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3552000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3380000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3341000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1315000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2288000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2715000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2587000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>895000</v>
+      </c>
+      <c r="E43" s="3">
         <v>947000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>835000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>852000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>873000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>894000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>779000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>814000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>880000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1038000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>848000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>712000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>755000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>789000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>647000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>655000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>687000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>730000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>693000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>787000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>788000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>777000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>796000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>824000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>894000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>813000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>828000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>908000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>883000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>858000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>851000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>784000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>892000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>906000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>827000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>937000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>871000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>618000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>669000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>689000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1360000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1372000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1044000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>965000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>993000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>991000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1113000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1059000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1042000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1192000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1240000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2160000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2376000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2324000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11190000</v>
+      </c>
+      <c r="E46" s="3">
         <v>10589000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9511000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10947000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11220000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9380000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9720000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11037000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11362000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10669000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7709000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10662000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10566000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9509000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,297 +5024,306 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>83663000</v>
+      </c>
+      <c r="E47" s="3">
         <v>84094000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>85265000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>89108000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>90980000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>88315000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>85505000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>94046000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>85702000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>90461000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>94982000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>90353000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>95489000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>100588000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>113454000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>109818000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>116242000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>128324000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>137927000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>139796000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>141240000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>138299000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>144612000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>140566000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>136705000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>132819000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>133195000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>135294000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>133578000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>127546000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>121906000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>120785000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>124074000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>128591000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>120168000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>117562000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>117632000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>116298000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>111502000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>123665000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E48" s="3">
         <v>354000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>351000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>367000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>390000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>391000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>387000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>421000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>398000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>418000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>445000</v>
       </c>
       <c r="N48" s="3">
         <v>445000</v>
       </c>
       <c r="O48" s="3">
+        <v>445000</v>
+      </c>
+      <c r="P48" s="3">
         <v>500000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>528000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>530000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>488000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>512000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>538000</v>
       </c>
       <c r="U48" s="3">
         <v>538000</v>
       </c>
       <c r="V48" s="3">
+        <v>538000</v>
+      </c>
+      <c r="W48" s="3">
         <v>542000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>563000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>578000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>601000</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>584000</v>
       </c>
       <c r="AA48" s="3">
         <v>584000</v>
       </c>
       <c r="AB48" s="3">
+        <v>584000</v>
+      </c>
+      <c r="AC48" s="3">
         <v>586000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>581000</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>562000</v>
       </c>
       <c r="AE48" s="3">
         <v>562000</v>
       </c>
       <c r="AF48" s="3">
+        <v>562000</v>
+      </c>
+      <c r="AG48" s="3">
         <v>559000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>443000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>435000</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>448000</v>
       </c>
       <c r="AJ48" s="3">
         <v>448000</v>
       </c>
       <c r="AK48" s="3">
+        <v>448000</v>
+      </c>
+      <c r="AL48" s="3">
         <v>434000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>439000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>442000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>444000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>433000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>476000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8948000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8976000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9294000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9216000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9296000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9083000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9021000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9232000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8550000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8819000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9397000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8771000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8860000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9267000</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -5289,8 +5399,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2251000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2292000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2074000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2314000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2365000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2222000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1861000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1941000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2166000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1812000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1450000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1806000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1663000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1532000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>115961000</v>
+      </c>
+      <c r="E54" s="3">
         <v>116280000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>116470000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122306000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>124736000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>120258000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117566000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>128442000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120168000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>124742000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>126724000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>125111000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>130626000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>134966000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>131738000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>128100000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>135629000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>147046000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>157542000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>160597000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>161492000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>158157000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>165086000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>160955000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>157087000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>151616000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>152768000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>154137000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>151400000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>145679000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>140406000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>137941000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>141986000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>147356000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>137217000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>136083000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>135394000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>133650000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>129819000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>144101000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>553000</v>
+      </c>
+      <c r="E57" s="3">
         <v>522000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>495000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>460000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>426000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>411000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>381000</v>
       </c>
       <c r="J57" s="3">
         <v>381000</v>
       </c>
       <c r="K57" s="3">
+        <v>381000</v>
+      </c>
+      <c r="L57" s="3">
         <v>359000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>344000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>261000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>249000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>244000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>229000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8115000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6855000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4916000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6059000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6128000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3928000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2445000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4559000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4944000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3849000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2133000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5243000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5270000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3943000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,175 +6364,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3880000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3945000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3474000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3529000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2651000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2853000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2463000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2542000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2841000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2775000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2616000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3346000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2777000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2965000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11114000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12121000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13619000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14854000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16254000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17642000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18086000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16944000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17189000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17283000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>18983000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19194000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>18955000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>20016000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19087000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>19317000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>17308000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>18055000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>20521000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>23276000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>18249000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>19946000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>20245000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>20878000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>19488000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>23347000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12548000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11322000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8885000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10048000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9205000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7192000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5289000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7482000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8144000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6968000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5010000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8838000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8291000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7137000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8061000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7609000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7671000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8286000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8847000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7269000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7419000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7891000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7430000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7912000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7153000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6961000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7087000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7420000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7303000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7401000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7288000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7638000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7851000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7950000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7992000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7951000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7756000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7686000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7629000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6609000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6420000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6108000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6110000</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>5778000</v>
       </c>
       <c r="AG61" s="3">
         <v>5778000</v>
       </c>
       <c r="AH61" s="3">
+        <v>5778000</v>
+      </c>
+      <c r="AI61" s="3">
         <v>5279000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5315000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5372000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5289000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5248000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5252000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5250000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5360000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5765000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>64758000</v>
+      </c>
+      <c r="E62" s="3">
         <v>67094000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>70140000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>75136000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>79330000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>79307000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>78469000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>88074000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>78399000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>86164000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>92401000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>86053000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>94189000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>99943000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>85649000</v>
+      </c>
+      <c r="E66" s="3">
         <v>86319000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86980000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>93618000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>97536000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>93920000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>91468000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>103612000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>94121000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>101205000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>104739000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>102442000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>110187000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>115182000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>111598000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>103948000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>109242000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>117519000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>124289000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>127045000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>127757000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>126054000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>131527000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>128476000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>127667000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>125214000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>123809000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>124699000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>123159000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>119630000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>116944000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>114707000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>118186000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>123069000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>112619000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>114106000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>113891000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>113310000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>109337000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>121316000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>56218000</v>
+      </c>
+      <c r="E72" s="3">
         <v>55702000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>54682000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>53923000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>52595000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>52308000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52277000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50972000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51345000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>49872000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>47993000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48257000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>46937000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>45555000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>44367000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>44892000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>43547000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42413000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41381000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>40830000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>40162000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39277000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37984000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37460000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35204000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>34599000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>34291000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>33710000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33130000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32513000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>31788000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>31461000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>30809000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>30183000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>29895000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>27489000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>26942000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>26400000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>25981000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>25404000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30312000</v>
+      </c>
+      <c r="E76" s="3">
         <v>29961000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>29490000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>28688000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>27200000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26338000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26098000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24830000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26047000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23537000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21985000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22669000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20439000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19784000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20140000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24152000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26387000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>29527000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>33253000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>33552000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>33735000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>32103000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>33559000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>32479000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29420000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>26402000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>28959000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>29438000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>28241000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>26049000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23462000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23234000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>23800000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>24287000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>24598000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>21977000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>21503000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>20340000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>20482000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>22785000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>825000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1019000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1379000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1639000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>599000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1902000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-93000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1755000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1879000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>268000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1569000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1634000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1188000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>196000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1781000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1394000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1047000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1039000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>888000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1105000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1293000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>952000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2456000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>805000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>566000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>781000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>777000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>817000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>928000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>525000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>845000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>832000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>717000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2583000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>716000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>713000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>592000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>751000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>629000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,113 +8961,114 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E83" s="3">
         <v>6000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>32000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>39000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>45000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
         <v>294000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>268000</v>
       </c>
       <c r="S83" s="3">
         <v>268000</v>
       </c>
       <c r="T83" s="3">
+        <v>268000</v>
+      </c>
+      <c r="U83" s="3">
         <v>322000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>301000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>277000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>281000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>311000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>300000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>292000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>289000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>333000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>315000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>318000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>309000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>340000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>313000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>315000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>303000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>314000</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL83" s="3" t="s">
         <v>8</v>
       </c>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E89" s="3">
         <v>968000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>315000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1252000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>399000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>589000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>333000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1270000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>255000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>849000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>582000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1276000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>442000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>890000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1033000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1076000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>510000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1260000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>870000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1853000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>962000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1366000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1357000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2000000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1187000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1414000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1192000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1906000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>813000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1544000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1355000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1852000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1569000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1238000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1532000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1431000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1408000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1757000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1867000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1266000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>791000</v>
+      </c>
+      <c r="E94" s="3">
         <v>244000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>359000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>28000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1533000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-359000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1517000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1030000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2067000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>227000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>490000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1565000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-693000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-930000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1293000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1210000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1207000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-332000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>130000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-969000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1108000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1391000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-404000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1716000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-225000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-219000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1291000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-410000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-199000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2544000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-370000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-990000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1527000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1217000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E96" s="3">
         <v>304000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>292000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>299000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>301000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>306000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>267000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>270000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>272000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>278000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>236000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>239000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>243000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>248000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-239000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-242000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-248000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-250000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-208000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-217000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-211000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-219000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-189000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-192000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-193000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-194000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-198000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-199000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-201000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-170000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-162000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-166000</v>
       </c>
       <c r="AO96" s="3">
         <v>-166000</v>
       </c>
       <c r="AP96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-162000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-442000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1762000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1184000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1462000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-162000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1261000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1084000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-826000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-256000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-787000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-992000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1011000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-933000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1295000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-612000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-907000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-737000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-842000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-756000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-671000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-470000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-684000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-583000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>598000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-446000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-451000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-292000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-686000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-103000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-525000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-515000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-473000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-452000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-382000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-355000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-876000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-784000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>446000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E101" s="3">
         <v>33000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-149000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>138000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-40000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-28000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>170000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>8000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-85000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>188000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-89000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>188000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-89000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>22000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-26000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>58000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-78000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>13000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>9000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>42000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>66000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>23000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>28000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-277000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>466000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-591000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-523000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-197000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1734000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-998000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>617000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-448000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>962000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>792000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1196000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>782000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>911000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-134000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-767000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-463000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>898000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-776000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1157000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>739000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>479000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-151000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-422000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>35000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1380000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-748000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>680000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1197000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-873000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-445000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>908000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-418000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-233000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>589000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>663000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>59000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-654000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-411000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1570000</v>
       </c>
     </row>
